--- a/data/trans_orig/IP31C_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_R_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74607</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>185</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,107 +1063,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>123233</t>
+          <t>108149</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125649</t>
+          <t>111752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>133</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>122558</t>
+          <t>91995</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116299</t>
+          <t>80294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124944</t>
+          <t>96341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>245792</t>
+          <t>200145</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239648</t>
+          <t>188365</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249307</t>
+          <t>206725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114532</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114532</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114532</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>213866</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>213866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>213866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1519,67 +1519,67 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55552</t>
+          <t>55743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63993</t>
+          <t>52827</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61983</t>
+          <t>49541</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1589,37 +1589,37 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>182</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>119545</t>
+          <t>108571</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116753</t>
+          <t>104620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>110765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21617</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32764</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>54712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>59846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>121081</t>
+          <t>114628</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111738</t>
+          <t>105269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128773</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>144502</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144502</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144502</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4194</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7774</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3356</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6632</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35385</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>31805</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>37577</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>37363</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>34087</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39528</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>83,71%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>130</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>71563</t>
+          <t>70754</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68027</t>
+          <t>67420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73740</t>
+          <t>72948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3442</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4268</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>43622</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>40848</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>43651</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>40018</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>44286</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>53782</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>160</t>
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>97404</t>
+          <t>90860</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>88435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,107 +2778,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>39484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>113036</t>
+          <t>121519</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107170</t>
+          <t>112815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117336</t>
+          <t>128063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>136390</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142715</t>
+          <t>113698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>249426</t>
+          <t>230718</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>239522</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258143</t>
+          <t>239588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>139709</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>139709</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>139709</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123027</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123027</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123027</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154235</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154235</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154235</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>277262</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277262</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>277262</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,107 +3121,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>33627</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>24369</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>44392</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>28,34%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>20470</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>14148</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>28572</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>31346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63891</t>
+          <t>69321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -3234,107 +3234,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>123037</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>112272</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>132295</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>71,66%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>84,44%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>107291</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>99189</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>113613</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>77,64%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>122414</t>
+          <t>114643</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>105774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130862</t>
+          <t>121926</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>315</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>229704</t>
+          <t>237680</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>217444</t>
+          <t>224463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>240645</t>
+          <t>249200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>156664</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>156664</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>156664</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>127761</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>127761</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>127761</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>293784</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>293784</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>293784</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,107 +3464,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>73643</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>113299</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>153988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -3577,107 +3577,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>842</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>602974</t>
+          <t>611755</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>589931</t>
+          <t>594838</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>614786</t>
+          <t>624783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>839</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>677547</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>662267</t>
+          <t>542670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>690632</t>
+          <t>570142</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1280521</t>
+          <t>1168540</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1259794</t>
+          <t>1147396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1297804</t>
+          <t>1188085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
